--- a/static/templates/workbook.xlsx
+++ b/static/templates/workbook.xlsx
@@ -9406,7 +9406,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>не установлено — вопрос в анкете министерству</t>
+          <t>не установлено — вопрос в анкете центру</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>wait-list-region-c</t>
+          <t>region-c-waiting-list</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
